--- a/agent_runs/manjidiwang/episodes/ep11/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep11/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>车内警报（，总时长：10秒，镜头数：5个）</t>
+          <t>车内警报</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>致命追击（，总时长：10秒，镜头数：4个）</t>
+          <t>致命追击</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>失控甩尾（，总时长：10秒，镜头数：4个）</t>
+          <t>失控甩尾</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>悬崖绝境（，总时长：14秒，镜头数：6个）</t>
+          <t>悬崖绝境</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>致命撞击（，总时长：10秒，镜头数：4个）</t>
+          <t>致命撞击</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>坠落与遗言（，总时长：10秒，镜头数：4个）</t>
+          <t>坠落与遗言</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>崖底救援（，总时长：12秒，镜头数：5个）</t>
+          <t>崖底救援</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>底牌与誓言（，总时长：14秒，镜头数：5个）</t>
+          <t>底牌与誓言</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>梦呓与托付（，总时长：10秒，镜头数：4个）</t>
+          <t>梦呓与托付</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>修罗令（，总时长：11秒，镜头数：4个）</t>
+          <t>修罗令</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
